--- a/dev/StructureDefinition-bc-practitioner-relationship-extension.xlsx
+++ b/dev/StructureDefinition-bc-practitioner-relationship-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1261,7 +1261,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>103</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>117</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>124</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>129</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>131</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>136</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>137</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>142</v>
       </c>
@@ -3343,12 +3343,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK24">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
